--- a/题库/PY理论2026-05-21-08-58.xlsx
+++ b/题库/PY理论2026-05-21-08-58.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="198">
   <si>
     <t>题号</t>
   </si>
@@ -68,7 +68,8 @@
     <t>单选</t>
   </si>
   <si>
-    <t>以下选项中，符合Python语言变量命名规则的是（）。</t>
+    <t>1.
+以下选项中，符合Python语言变量命名规则的是（）。</t>
   </si>
   <si>
     <t>Templist</t>
@@ -95,7 +96,8 @@
     <t>2</t>
   </si>
   <si>
-    <t>在下列语句中,定义了一个Python字典的是（ ）。</t>
+    <t>2.
+在下列语句中,定义了一个Python字典的是（ ）。</t>
   </si>
   <si>
     <t>[1,2,3]</t>
@@ -116,7 +118,8 @@
     <t>3</t>
   </si>
   <si>
-    <t>以下不能创建字典的语句是（）。</t>
+    <t>3.
+以下不能创建字典的语句是（）。</t>
   </si>
   <si>
     <t>dict={}</t>
@@ -134,7 +137,8 @@
     <t>4</t>
   </si>
   <si>
-    <t>Python文件的后缀名是（ ）</t>
+    <t>4.
+Python文件的后缀名是（  ）</t>
   </si>
   <si>
     <t>py</t>
@@ -152,7 +156,8 @@
     <t>5</t>
   </si>
   <si>
-    <t>下面（ ）不是"+"的用法。</t>
+    <t>5.
+下面（ ）不是"+"的用法。</t>
   </si>
   <si>
     <t>字符串连接</t>
@@ -173,7 +178,8 @@
     <t>6</t>
   </si>
   <si>
-    <t>对于列表L=[1,2,'Python',[1,2,3,4,5]],L[-3]的是（）。</t>
+    <t>6.
+对于列表L=[1,2,'Python',[1,2,3,4,5]],L[-3]的是（）。</t>
   </si>
   <si>
     <t>'Python'</t>
@@ -188,10 +194,13 @@
     <t>7</t>
   </si>
   <si>
-    <t>执行下列语句后的显示结果是（）。 world="world" print("hello"+world)</t>
-  </si>
-  <si>
-    <t>helloword</t>
+    <t>7.
+执行下列语句后的显示结果是（）。
+world="world"
+print("hello"+world)</t>
+  </si>
+  <si>
+    <t>helloworld</t>
   </si>
   <si>
     <t>"hello"world</t>
@@ -206,7 +215,8 @@
     <t>8</t>
   </si>
   <si>
-    <t>x="3.1415926"，以下哪个选项表示"3.14"()?</t>
+    <t>8.
+x="3.1415926"，以下哪个选项表示"3.14"()?</t>
   </si>
   <si>
     <t>x[0:3]</t>
@@ -224,7 +234,8 @@
     <t>9</t>
   </si>
   <si>
-    <t>下面（ ）不是合法的整数数字。</t>
+    <t>9.
+下面（ ）不是合法的整数数字。</t>
   </si>
   <si>
     <t>0x1e</t>
@@ -242,7 +253,11 @@
     <t>10</t>
   </si>
   <si>
-    <t>下列语句执行后的结果是（）。 fruits={'apple': 3,'banana': 4,'pear':5} fruits['banana']=7 print(sum(fruits.values()))</t>
+    <t>10.
+下列语句执行后的结果是（）。
+fruits={'apple': 3,'banana': 4,'pear':5}
+fruits['banana']=7
+print(sum(fruits.values()))</t>
   </si>
   <si>
     <t>19</t>
@@ -257,7 +272,8 @@
     <t>11</t>
   </si>
   <si>
-    <t>下列转义字符能够实现换行的是()。</t>
+    <t>11.
+下列转义字符能够实现换行的是()。</t>
   </si>
   <si>
     <t>\b</t>
@@ -272,7 +288,8 @@
     <t>\t</t>
   </si>
   <si>
-    <t>关于 while 循环和 for循环的区别, 下列叙述正确的是 ( ) 。</t>
+    <t>12.
+关于 while 循环和 for循环的区别, 下列叙述正确的是 (   ) 。</t>
   </si>
   <si>
     <t>while 语句的循环体至少无条件执行一次，for语句的循环体有可能一次都不执行</t>
@@ -290,7 +307,8 @@
     <t>13</t>
   </si>
   <si>
-    <t>欲将两数中较小的数返回，应定义的匿名函数为（）。</t>
+    <t>13.
+欲将两数中较小的数返回，应定义的匿名函数为（）。</t>
   </si>
   <si>
     <t>mymin=lambda x,y: x if x&gt;=y else y</t>
@@ -308,7 +326,9 @@
     <t>14</t>
   </si>
   <si>
-    <t>下面代码的输出结果是（）。 x=0x1010;print(x)</t>
+    <t>14.
+下面代码的输出结果是（）。
+x=0x1010;print(x)</t>
   </si>
   <si>
     <t>4112</t>
@@ -320,7 +340,8 @@
     <t>520</t>
   </si>
   <si>
-    <t>以下选项中，不属于函数作用的是 ( )。</t>
+    <t>15.
+以下选项中，不属于函数作用的是 (   )。</t>
   </si>
   <si>
     <t>区分全局变量和局部变量</t>
@@ -338,7 +359,10 @@
     <t>16</t>
   </si>
   <si>
-    <t>下列程序执行后，y的值是（）。 def f(x,y): return x2+y2</t>
+    <t>16.
+下列程序执行后，y的值是（）。
+def f(x,y):
+    return x2+y2</t>
   </si>
   <si>
     <t>100</t>
@@ -353,7 +377,8 @@
     <t>17</t>
   </si>
   <si>
-    <t>str(int(3.14))结果为（ ）。</t>
+    <t>17.
+str(int(3.14))结果为（ ）。</t>
   </si>
   <si>
     <t>3.14</t>
@@ -371,7 +396,10 @@
     <t>18</t>
   </si>
   <si>
-    <t>下面代码的输出结果是（）。 &gt;&gt;&gt; a = b = c =123 &gt;&gt;&gt; print(a,b,c)</t>
+    <t>18.
+下面代码的输出结果是（）。
+&gt;&gt;&gt; a = b = c =123
+&gt;&gt;&gt; print(a,b,c)</t>
   </si>
   <si>
     <t>0 0 123</t>
@@ -386,7 +414,8 @@
     <t>1 1 123</t>
   </si>
   <si>
-    <t>以下关于Python分支结构的描述中， 错误的是()。</t>
+    <t>19.
+以下关于Python分支结构的描述中， 错误的是()。</t>
   </si>
   <si>
     <t>Python分支结构使用保留字if、elif和else来实现， 每个if后面必须有elif或else</t>
@@ -404,7 +433,8 @@
     <t>20</t>
   </si>
   <si>
-    <t>下面（ ）是非法变量名。</t>
+    <t>20.
+下面（ ）是非法变量名。</t>
   </si>
   <si>
     <t>my-name</t>
@@ -425,91 +455,109 @@
     <t>填空</t>
   </si>
   <si>
-    <t>Python中定义函数的关键字是【1】。</t>
-  </si>
-  <si>
-    <t>def</t>
+    <t>21.
+Python中定义函数的关键字是【1】。</t>
+  </si>
+  <si>
+    <t>(1) def</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>"4"+"5"的值是【1】。</t>
-  </si>
-  <si>
-    <t>45或'45'或"45"</t>
+    <t>22.
+"4"+"5"的值是【1】。</t>
+  </si>
+  <si>
+    <t>(1) 45;
+"45";
+'45'</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>在Python中，传统除法运算符是【1】，整除除法运算符是【2】。</t>
-  </si>
-  <si>
-    <t>/;//</t>
+    <t>23.
+在Python中，传统除法运算符是【1】，整除除法运算符是【2】。</t>
+  </si>
+  <si>
+    <t>(1) /;//</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>Python的数字有4种数据类型：整数、浮点数、布尔值和【1】。</t>
-  </si>
-  <si>
-    <t>复数</t>
+    <t>24.
+Python的数字有4种数据类型：整数、浮点数、布尔值和【1】。</t>
+  </si>
+  <si>
+    <t>(1) 复数</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>表达式[1, 2, 3]*3的执行结果为【1】。</t>
-  </si>
-  <si>
-    <t>[1, 2, 3, 1, 2, 3, 1, 2, 3]</t>
+    <t>25.
+表达式[1, 2, 3]*3的执行结果为【1】。</t>
+  </si>
+  <si>
+    <t>(1) [1, 2, 3, 1, 2, 3, 1, 2, 3]</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>设有f=lambda x,y:{x:y},则f(5,10)的值是【1】。</t>
-  </si>
-  <si>
-    <t>{5:10}</t>
+    <t>26.
+设有f=lambda x,y:{x:y},则f(5,10)的值是【1】。</t>
+  </si>
+  <si>
+    <t>(1) {5:10}</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>下列Python 语句的输出结果是【1】。 def judge(p1,*p2): print(p2) judge(1,2,3,4,5)</t>
-  </si>
-  <si>
-    <t>(2,3,4,5)</t>
+    <t>27.
+下列Python 语句的输出结果是【1】。
+def judge(p1,*p2):
+    print(p2)
+judge(1,2,3,4,5)</t>
+  </si>
+  <si>
+    <t>(1) (2,3,4,5)</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>切片操作list(range(6))[::2]执行结果为【1】。</t>
-  </si>
-  <si>
-    <t>[0,2,4]</t>
+    <t>28.
+切片操作list(range(6))[::2]执行结果为【1】。</t>
+  </si>
+  <si>
+    <t>(1) [0,2,4]</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>在Python语言中单分支结构可以用【1】语句。</t>
-  </si>
-  <si>
-    <t>if</t>
+    <t>29.
+在Python语言中单分支结构可以用【1】语句。</t>
+  </si>
+  <si>
+    <t>(1) if</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>下列Python语句的运行结果为【1】。 for i in range(1,3):print(i,end='') for i in range(2,5):print(i,end='')</t>
-  </si>
-  <si>
-    <t>12234</t>
+    <t>30.
+下列Python语句的运行结果为【1】。
+for i in range(1,3):print(i,end='')
+for i in range(2,5):print(i,end='')</t>
+  </si>
+  <si>
+    <t>(1) 
+12234</t>
   </si>
   <si>
     <t>31</t>
@@ -518,7 +566,8 @@
     <t>判断</t>
   </si>
   <si>
-    <t>当作为条件表达式时，空值、空字符串、空列表、空元组、空字典、空集合、空迭代对象以及任意形式的数字0都等价于 False。</t>
+    <t>31.
+当作为条件表达式时，空值、空字符串、空列表、空元组、空字典、空集合、空迭代对象以及任意形式的数字0都等价于 False。</t>
   </si>
   <si>
     <t>正确</t>
@@ -527,64 +576,67 @@
     <t>错误</t>
   </si>
   <si>
-    <t>对</t>
-  </si>
-  <si>
     <t>2.4</t>
   </si>
   <si>
     <t>32</t>
   </si>
   <si>
-    <t>在循环中 continue I语句的作用是跳出当前循环。</t>
-  </si>
-  <si>
-    <t>错</t>
+    <t>32.
+在循环中 continue I语句的作用是跳出当前循环。</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>在Python中0xad是合法的十六进制数字表示形式。</t>
+    <t>33.
+在Python中0xad是合法的十六进制数字表示形式。</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>已知x是个列表对象，那么执行语句y＝x之后，对y所做的任何操作都会同样作用到x上。</t>
-  </si>
-  <si>
-    <t>Python集合可以包含相同的元素。</t>
+    <t>34.
+已知x是个列表对象，那么执行语句y＝x之后，对y所做的任何操作都会同样作用到x上。</t>
+  </si>
+  <si>
+    <t>35.
+Python集合可以包含相同的元素。</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>只能通过切片访回元组中的元素，不能使用切片修改元组中的元素。</t>
+    <t>36.
+只能通过切片访回元组中的元素，不能使用切片修改元组中的元素。</t>
   </si>
   <si>
     <t>37</t>
   </si>
   <si>
-    <t>表达式pow(3, 2) == 3 2的值为True。</t>
+    <t>37.
+表达式pow(3, 2) == 3 2的值为True。</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>列表、元组、字符串属于有序序列，而字典和集合属于无序序列。</t>
+    <t>38.
+列表、元组、字符串属于有序序列，而字典和集合属于无序序列。</t>
   </si>
   <si>
     <t>39</t>
   </si>
   <si>
-    <t>无法使用lambda表达式定义有名字的函数。</t>
+    <t>39.
+无法使用lambda表达式定义有名字的函数。</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>在Python中，不能在一个函数的定义中再定义一个嵌套函数。</t>
+    <t>40.
+在Python中，不能在一个函数的定义中再定义一个嵌套函数。</t>
   </si>
   <si>
     <t>41</t>
@@ -593,25 +645,58 @@
     <t>程序填空</t>
   </si>
   <si>
-    <t>'''------------------------------------------------------ 【程序填空】 --------------------------------------------------------- 题目：输入3个整数x、y、z，请把这3个数由小到大输出。 ------------------------------------------------------------ 注意：除要求填空的位置之外，请勿改动程序中的其他内容。 ------------------------------------------------------''' #***********SPACE********** l=【1】 for i in range(3): x=int(input("请输入一个数:")) l.append(x) #************SPACE************ 【2】 print(l)</t>
-  </si>
-  <si>
-    <t>(1)[]; (2)l.sort()</t>
-  </si>
-  <si>
-    <t>ProgPy11.py</t>
+    <t>41.
+'''------------------------------------------------------
+【程序填空】
+---------------------------------------------------------
+题目：输入3个整数x、y、z，请把这3个数由小到大输出。
+------------------------------------------------------------
+注意：除要求填空的位置之外，请勿改动程序中的其他内容。
+------------------------------------------------------'''
+#***********SPACE**********
+l=【1】
+for i in range(3):
+    x=int(input("请输入一个数:"))
+    l.append(x)
+#************SPACE************
+【2】
+print(l)</t>
+  </si>
+  <si>
+    <t>(1) [] | (2) l.sort()</t>
+  </si>
+  <si>
+    <t>ProgPy50.py</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>'''------------------------------------------------------ 【程序填空】 --------------------------------------------------------- 题目：通过循环计算并输出满足条件的正方体的体积： 正方体棱长从1开始到10依次计算，当体积大于100时停止输出。 ------------------------------------------------------------ 注意：除要求填空的位置之外，请勿改动程序中的其他内容。 ------------------------------------------------------''' i=1 #**************SPACE************ while 【1】: v=iii print(i,v) if v&gt;100: #***********SPACE**************** 【2】 i=i+1</t>
-  </si>
-  <si>
-    <t>(1)i&lt;=10或i&lt;11; (2)break</t>
-  </si>
-  <si>
-    <t>ProgPy12.py</t>
+    <t>42.
+'''------------------------------------------------------
+【程序填空】
+---------------------------------------------------------
+题目：通过循环计算并输出满足条件的正方体的体积：
+正方体棱长从1开始到10依次计算，当体积大于100时停止输出。
+------------------------------------------------------------
+注意：除要求填空的位置之外，请勿改动程序中的其他内容。
+------------------------------------------------------'''
+i=1
+#**************SPACE************
+while 【1】:
+    v=iii
+    print(i,v)
+    if v&gt;100:
+#***********SPACE****************
+        【2】
+    i=i+1</t>
+  </si>
+  <si>
+    <t>(1) i&lt;=10;
+i&lt;11 | (2) break</t>
+  </si>
+  <si>
+    <t>ProgPy51.py</t>
   </si>
   <si>
     <t>43</t>
@@ -620,13 +705,38 @@
     <t>程序改错</t>
   </si>
   <si>
-    <t>'''------------------------------------------------------ 【程序改错】 --------------------------------------------------------- 题目：将一个正整数分解质因数。例如：输入90,打印出90=2*3*3*5。 --------------------------------------------------------- 注意：不可以增加或删除程序行，也不可以更改程序的结构。 ------------------------------------------------------''' def main(): x=input("输入一个正整数:") #**************FOUND**************** if x.isdigit() and int(x)&lt;0: x=int(x) t,i=1,2 print(x,end="=") #******************FOUND************* while t&gt;0 if x%i==0: print(i,end="") x/=i #*****************FOUND*************** t=x+i if x!=1: print("",end="") while x%i and x!=1: i+=1 else: print("请输入正确的正整数") if __name__ == '__main__': main()</t>
-  </si>
-  <si>
-    <t>(1)if x.isdigit() and int(x)&gt;0:; (2)while t&gt;=0:; (3)t=x-i或t=-i+x</t>
-  </si>
-  <si>
-    <t>ProgPy13.py</t>
+    <t>43.
+'''------------------------------------------------------
+【程序改错】
+---------------------------------------------------------
+题目：将一个正整数分解质因数。例如：输入90,打印出90=2*3*3*5。
+---------------------------------------------------------
+注意：不可以增加或删除程序行，也不可以更改程序的结构。
+------------------------------------------------------'''
+def main():
+    x=input("输入一个正整数:")
+#**************FOUND****************
+    if x.isdigit() and int(x)0
+            if x%i==0:
+                print(i,end="")
+                x/=i
+#*****************FOUND***************
+            t=x+i
+            if x!=1:
+                print("",end="")
+            while x%i and x!=1:
+                i+=1
+    else:
+        print("请输入正确的正整数")
+if __name__ == '__main__':
+    main()</t>
+  </si>
+  <si>
+    <t>(1) if x.isdigit() and int(x)&gt;0: | (2) while t&gt;=0: | (3) t=x-i;
+t=-i+x</t>
+  </si>
+  <si>
+    <t>ProgPy52.py</t>
   </si>
 </sst>
 </file>
@@ -1095,154 +1205,162 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1627,26 +1745,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" ht="98" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -1662,26 +1780,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" ht="98" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1697,26 +1815,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" ht="70" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -1732,26 +1850,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" ht="70" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1767,26 +1885,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" ht="70" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -1802,26 +1920,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" ht="112" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -1837,26 +1955,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" ht="140" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>57</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -1872,26 +1990,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" ht="98" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -1907,26 +2025,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" ht="70" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -1942,26 +2060,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" ht="266" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -1977,26 +2095,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" ht="70" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -2012,26 +2130,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" ht="126" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H13" s="1" t="s">
@@ -2047,26 +2165,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" ht="98" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -2082,26 +2200,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" ht="112" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>96</v>
       </c>
       <c r="H15" s="1" t="s">
@@ -2117,26 +2235,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" ht="84" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H16" s="1" t="s">
@@ -2152,26 +2270,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" ht="140" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -2187,26 +2305,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" ht="70" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H18" s="1" t="s">
@@ -2222,26 +2340,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" ht="154" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>118</v>
       </c>
       <c r="H19" s="1" t="s">
@@ -2257,26 +2375,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" ht="98" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>123</v>
       </c>
       <c r="H20" s="1" t="s">
@@ -2292,26 +2410,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" ht="56" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>129</v>
       </c>
       <c r="H21" s="1" t="s">
@@ -2327,16 +2445,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" ht="84" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>132</v>
       </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
       <c r="H22" s="1" t="s">
         <v>133</v>
       </c>
@@ -2350,16 +2472,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" ht="56" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
       <c r="H23" s="1" t="s">
         <v>136</v>
       </c>
@@ -2373,16 +2499,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" ht="126" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="1" t="s">
         <v>139</v>
       </c>
@@ -2396,16 +2526,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" ht="126" spans="1:11">
       <c r="A25" s="1" t="s">
         <v>140</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
       <c r="H25" s="1" t="s">
         <v>142</v>
       </c>
@@ -2419,16 +2553,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" ht="84" spans="1:11">
       <c r="A26" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>144</v>
       </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
       <c r="H26" s="1" t="s">
         <v>145</v>
       </c>
@@ -2442,16 +2580,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" ht="112" spans="1:11">
       <c r="A27" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>147</v>
       </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="1" t="s">
         <v>148</v>
       </c>
@@ -2465,16 +2607,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" ht="210" spans="1:11">
       <c r="A28" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>150</v>
       </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
       <c r="H28" s="1" t="s">
         <v>151</v>
       </c>
@@ -2488,16 +2634,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" ht="112" spans="1:11">
       <c r="A29" s="1" t="s">
         <v>152</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
       <c r="H29" s="1" t="s">
         <v>154</v>
       </c>
@@ -2511,16 +2661,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" ht="98" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>156</v>
       </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="1" t="s">
         <v>157</v>
       </c>
@@ -2534,16 +2688,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" ht="224" spans="1:11">
       <c r="A31" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>159</v>
       </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="1" t="s">
         <v>160</v>
       </c>
@@ -2557,14 +2715,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" ht="224" spans="1:11">
       <c r="A32" s="1" t="s">
         <v>161</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>163</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -2573,28 +2731,30 @@
       <c r="E32" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
       <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="J32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" ht="98" spans="1:11">
+      <c r="A33" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>169</v>
+      <c r="C33" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>164</v>
@@ -2602,11 +2762,13 @@
       <c r="E33" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
       <c r="H33" s="1" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>20</v>
@@ -2615,15 +2777,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" ht="98" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>172</v>
+      <c r="C34" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>164</v>
@@ -2631,12 +2793,14 @@
       <c r="E34" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="J34" s="1" t="s">
         <v>20</v>
       </c>
@@ -2644,15 +2808,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" ht="168" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>174</v>
+      <c r="C35" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>164</v>
@@ -2660,12 +2824,14 @@
       <c r="E35" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="J35" s="1" t="s">
         <v>20</v>
       </c>
@@ -2673,15 +2839,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" ht="70" spans="1:11">
       <c r="A36" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>175</v>
+      <c r="C36" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>164</v>
@@ -2689,11 +2855,13 @@
       <c r="E36" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
       <c r="H36" s="1" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>20</v>
@@ -2702,15 +2870,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" ht="126" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>177</v>
+      <c r="C37" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>164</v>
@@ -2718,12 +2886,14 @@
       <c r="E37" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="J37" s="1" t="s">
         <v>20</v>
       </c>
@@ -2731,15 +2901,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" ht="84" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>179</v>
+      <c r="C38" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>164</v>
@@ -2747,12 +2917,14 @@
       <c r="E38" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
       <c r="H38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="J38" s="1" t="s">
         <v>20</v>
       </c>
@@ -2760,15 +2932,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" ht="126" spans="1:11">
       <c r="A39" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>181</v>
+      <c r="C39" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>164</v>
@@ -2776,12 +2948,14 @@
       <c r="E39" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="J39" s="1" t="s">
         <v>20</v>
       </c>
@@ -2789,15 +2963,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" ht="84" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>183</v>
+      <c r="C40" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>164</v>
@@ -2805,11 +2979,13 @@
       <c r="E40" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
       <c r="H40" s="1" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>20</v>
@@ -2818,15 +2994,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" ht="112" spans="1:11">
       <c r="A41" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>185</v>
+      <c r="C41" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>164</v>
@@ -2834,11 +3010,13 @@
       <c r="E41" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
       <c r="H41" s="1" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>20</v>
@@ -2847,70 +3025,82 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" ht="409.5" spans="1:11">
       <c r="A42" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="I42" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="K42" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" ht="409.5" spans="1:11">
+      <c r="A43" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J42" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="1" t="s">
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="K43" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" ht="409.5" spans="1:11">
+      <c r="A44" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="I44" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>20</v>
